--- a/data/raw/sales/Week 11/Nexlev/other_channels.xlsx
+++ b/data/raw/sales/Week 11/Nexlev/other_channels.xlsx
@@ -682,7 +682,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>ET-02</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D4" s="13" t="n">
@@ -738,7 +738,7 @@
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>ET-01 Black</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="D6" s="13" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D8" s="13" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>ET-01 Black</t>
+          <t>ET-01-BK</t>
         </is>
       </c>
       <c r="D12" s="14" t="n">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D16" s="14" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D17" s="14" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D19" s="14" t="n">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="C22" s="27" t="inlineStr">
         <is>
-          <t>EA-01 Pro</t>
+          <t>EA-01</t>
         </is>
       </c>
       <c r="D22" s="27" t="n">
@@ -3050,7 +3050,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ETC-07</t>
+          <t>ETC-07-WH</t>
         </is>
       </c>
       <c r="D37" s="3" t="n">
@@ -3900,7 +3900,7 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>V-01-RG</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="D43" s="3" t="n">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>GS-5</t>
+          <t>GS-05</t>
         </is>
       </c>
       <c r="D44" s="3" t="n">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C4" s="15" t="inlineStr">
         <is>
-          <t>ETC-05</t>
+          <t>ETC-05-PI</t>
         </is>
       </c>
       <c r="D4" s="15" t="n">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="D8" s="34" t="inlineStr">
         <is>
-          <t>V-01 Rose Gold</t>
+          <t>V-01 RG</t>
         </is>
       </c>
       <c r="E8" s="35" t="n">
@@ -5827,7 +5827,7 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="D54" s="34" t="inlineStr">
         <is>
-          <t>HD-02</t>
+          <t>HD-01</t>
         </is>
       </c>
       <c r="E54" s="35" t="n">
@@ -7027,7 +7027,7 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>ETC-04</t>
+          <t>ETC-04-WH</t>
         </is>
       </c>
       <c r="D3" s="17" t="n">
@@ -7239,7 +7239,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="17" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -7282,7 +7282,7 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>ET-02</t>
+          <t>ET-02-GN</t>
         </is>
       </c>
       <c r="D5" s="17" t="n">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>VC 02</t>
+          <t>VC-02</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="C7" s="17" t="inlineStr">
         <is>
-          <t>VC 04</t>
+          <t>VC-04</t>
         </is>
       </c>
       <c r="D7" s="17" t="n">
@@ -7998,7 +7998,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="20" t="inlineStr">
         <is>
-          <t>FBA79350</t>
+          <t>FBP79350</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>CFM-01</t>
+          <t>SC-01</t>
         </is>
       </c>
       <c r="D32" s="14" t="n">
